--- a/bodekasse.xlsx
+++ b/bodekasse.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1377"/>
+  <dimension ref="A1:R1386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -91481,6 +91481,600 @@
         <v>75</v>
       </c>
     </row>
+    <row r="1378">
+      <c r="A1378" s="21" t="inlineStr">
+        <is>
+          <t>Flø</t>
+        </is>
+      </c>
+      <c r="B1378" s="22" t="inlineStr">
+        <is>
+          <t>Efterår 2026</t>
+        </is>
+      </c>
+      <c r="C1378" s="22" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="D1378" s="22" t="inlineStr">
+        <is>
+          <t>Fulham FC</t>
+        </is>
+      </c>
+      <c r="E1378" s="22" t="inlineStr">
+        <is>
+          <t>Runde 3</t>
+        </is>
+      </c>
+      <c r="F1378" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1378" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1378" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1378" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1378" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1378" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1378" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="M1378" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="N1378" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1378" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1378" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1378" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1378" s="23" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="18" t="inlineStr">
+        <is>
+          <t>Frande</t>
+        </is>
+      </c>
+      <c r="B1379" s="19" t="inlineStr">
+        <is>
+          <t>Efterår 2026</t>
+        </is>
+      </c>
+      <c r="C1379" s="19" t="inlineStr">
+        <is>
+          <t>Arsenal FC</t>
+        </is>
+      </c>
+      <c r="D1379" s="19" t="inlineStr">
+        <is>
+          <t>Everton FC</t>
+        </is>
+      </c>
+      <c r="E1379" s="19" t="inlineStr">
+        <is>
+          <t>Runde 3</t>
+        </is>
+      </c>
+      <c r="F1379" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1379" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1379" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1379" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1379" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1379" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1379" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="M1379" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1379" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1379" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1379" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1379" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1379" s="20" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="21" t="inlineStr">
+        <is>
+          <t>Gulle</t>
+        </is>
+      </c>
+      <c r="B1380" s="22" t="inlineStr">
+        <is>
+          <t>Efterår 2026</t>
+        </is>
+      </c>
+      <c r="C1380" s="22" t="inlineStr">
+        <is>
+          <t>Manchester United FC</t>
+        </is>
+      </c>
+      <c r="D1380" s="22" t="inlineStr">
+        <is>
+          <t>Leeds United FC</t>
+        </is>
+      </c>
+      <c r="E1380" s="22" t="inlineStr">
+        <is>
+          <t>Runde 3</t>
+        </is>
+      </c>
+      <c r="F1380" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1380" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1380" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1380" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1380" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1380" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1380" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="M1380" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="N1380" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1380" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1380" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1380" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1380" s="23" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="18" t="inlineStr">
+        <is>
+          <t>Iver</t>
+        </is>
+      </c>
+      <c r="B1381" s="19" t="inlineStr">
+        <is>
+          <t>Efterår 2026</t>
+        </is>
+      </c>
+      <c r="C1381" s="19" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion FC</t>
+        </is>
+      </c>
+      <c r="D1381" s="19" t="inlineStr">
+        <is>
+          <t>Coventry City FC</t>
+        </is>
+      </c>
+      <c r="E1381" s="19" t="inlineStr">
+        <is>
+          <t>Runde 3</t>
+        </is>
+      </c>
+      <c r="F1381" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1381" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1381" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1381" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1381" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1381" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1381" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="M1381" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="N1381" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1381" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1381" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1381" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1381" s="20" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="21" t="inlineStr">
+        <is>
+          <t>Kragh</t>
+        </is>
+      </c>
+      <c r="B1382" s="22" t="inlineStr">
+        <is>
+          <t>Efterår 2026</t>
+        </is>
+      </c>
+      <c r="C1382" s="22" t="inlineStr">
+        <is>
+          <t>Aston Villa FC</t>
+        </is>
+      </c>
+      <c r="D1382" s="22" t="inlineStr">
+        <is>
+          <t>Nottingham Forest FC</t>
+        </is>
+      </c>
+      <c r="E1382" s="22" t="inlineStr">
+        <is>
+          <t>Runde 3</t>
+        </is>
+      </c>
+      <c r="F1382" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1382" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1382" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1382" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1382" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1382" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1382" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="M1382" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="N1382" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1382" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1382" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1382" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1382" s="23" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="18" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="B1383" s="19" t="inlineStr">
+        <is>
+          <t>Efterår 2026</t>
+        </is>
+      </c>
+      <c r="C1383" s="19" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
+      <c r="D1383" s="19" t="inlineStr">
+        <is>
+          <t>Newcastle United FC</t>
+        </is>
+      </c>
+      <c r="E1383" s="19" t="inlineStr">
+        <is>
+          <t>Runde 3</t>
+        </is>
+      </c>
+      <c r="F1383" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1383" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1383" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1383" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1383" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1383" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1383" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="M1383" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1383" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1383" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1383" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1383" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1383" s="20" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="21" t="inlineStr">
+        <is>
+          <t>Ole</t>
+        </is>
+      </c>
+      <c r="B1384" s="22" t="inlineStr">
+        <is>
+          <t>Efterår 2026</t>
+        </is>
+      </c>
+      <c r="C1384" s="22" t="inlineStr">
+        <is>
+          <t>Manchester City FC</t>
+        </is>
+      </c>
+      <c r="D1384" s="22" t="inlineStr">
+        <is>
+          <t>Ipswich Town FC</t>
+        </is>
+      </c>
+      <c r="E1384" s="22" t="inlineStr">
+        <is>
+          <t>Runde 3</t>
+        </is>
+      </c>
+      <c r="F1384" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1384" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1384" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1384" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1384" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1384" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1384" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="M1384" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="N1384" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1384" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1384" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1384" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1384" s="23" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="18" t="inlineStr">
+        <is>
+          <t>Rob</t>
+        </is>
+      </c>
+      <c r="B1385" s="19" t="inlineStr">
+        <is>
+          <t>Efterår 2026</t>
+        </is>
+      </c>
+      <c r="C1385" s="19" t="inlineStr">
+        <is>
+          <t>Brentford FC</t>
+        </is>
+      </c>
+      <c r="D1385" s="19" t="inlineStr">
+        <is>
+          <t>Crystal Palace FC</t>
+        </is>
+      </c>
+      <c r="E1385" s="19" t="inlineStr">
+        <is>
+          <t>Runde 3</t>
+        </is>
+      </c>
+      <c r="F1385" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1385" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1385" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1385" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1385" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1385" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1385" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="M1385" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1385" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1385" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1385" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1385" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1385" s="20" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="21" t="inlineStr">
+        <is>
+          <t>Strøm</t>
+        </is>
+      </c>
+      <c r="B1386" s="22" t="inlineStr">
+        <is>
+          <t>Efterår 2026</t>
+        </is>
+      </c>
+      <c r="C1386" s="22" t="inlineStr">
+        <is>
+          <t>Chelsea FC</t>
+        </is>
+      </c>
+      <c r="D1386" s="22" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur FC</t>
+        </is>
+      </c>
+      <c r="E1386" s="22" t="inlineStr">
+        <is>
+          <t>Runde 3</t>
+        </is>
+      </c>
+      <c r="F1386" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1386" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1386" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1386" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1386" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1386" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1386" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="M1386" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="N1386" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1386" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1386" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1386" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1386" s="23" t="n">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
